--- a/セリフ編集/その他セリフ/18-経営危機・エンディング.xlsx
+++ b/セリフ編集/その他セリフ/18-経営危機・エンディング.xlsx
@@ -576,7 +576,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.normal[1]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.standard[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -591,12 +591,12 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.normal[1]</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">enter.standard[1]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G12" t="inlineStr" s="3">
@@ -608,7 +608,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.normal[2]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.standard[2]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -623,12 +623,12 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.normal[2]</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">enter.standard[2]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G13" t="inlineStr" s="3">
@@ -2016,7 +2016,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.normal.high[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.high[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.high[1]</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">fighter.standard.high[1]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="3">
@@ -2048,7 +2048,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.normal.high[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.high[2]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.high[2]</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">fighter.standard.high[2]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G58" t="inlineStr" s="3">
@@ -2080,7 +2080,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.normal.high[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.high[3]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.high[3]</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">fighter.standard.high[3]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G59" t="inlineStr" s="3">
@@ -2112,7 +2112,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.normal.mid[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.mid[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.mid[1]</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">fighter.standard.mid[1]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G60" t="inlineStr" s="3">
@@ -2144,7 +2144,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.normal.mid[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.mid[2]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.mid[2]</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">fighter.standard.mid[2]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G61" t="inlineStr" s="3">
@@ -2176,7 +2176,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.normal.mid[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.mid[3]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.mid[3]</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">fighter.standard.mid[3]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G62" t="inlineStr" s="3">
@@ -2208,7 +2208,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.normal.low[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.low[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.low[1]</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">fighter.standard.low[1]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G63" t="inlineStr" s="3">
@@ -2240,7 +2240,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.normal.low[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.low[2]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.low[2]</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">fighter.standard.low[2]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G64" t="inlineStr" s="3">
@@ -2272,7 +2272,7 @@
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.normal.low[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.low[3]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.low[3]</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">fighter.standard.low[3]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G65" t="inlineStr" s="3">

--- a/セリフ編集/その他セリフ/18-経営危機・エンディング.xlsx
+++ b/セリフ編集/その他セリフ/18-経営危機・エンディング.xlsx
@@ -2466,7 +2466,7 @@
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.normal._default[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.normal[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal._default[1]</t>
+          <t xml:space="preserve">fighter._default.normal[1]</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="5">
@@ -2498,7 +2498,7 @@
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.normal._default[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.normal[2]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal._default[2]</t>
+          <t xml:space="preserve">fighter._default.normal[2]</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="5">
@@ -2530,7 +2530,7 @@
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.normal._default[3]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.normal[3]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal._default[3]</t>
+          <t xml:space="preserve">fighter._default.normal[3]</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="5">
@@ -2562,7 +2562,7 @@
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.bold._default[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.bold[1]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.bold._default[1]</t>
+          <t xml:space="preserve">fighter._default.bold[1]</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="6">
@@ -2594,7 +2594,7 @@
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.bold._default[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.bold[2]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.bold._default[2]</t>
+          <t xml:space="preserve">fighter._default.bold[2]</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="6">
@@ -2626,7 +2626,7 @@
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.bold._default[3]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.bold[3]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.bold._default[3]</t>
+          <t xml:space="preserve">fighter._default.bold[3]</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="6">
@@ -2658,7 +2658,7 @@
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.quiet._default[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.quiet[1]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.quiet._default[1]</t>
+          <t xml:space="preserve">fighter._default.quiet[1]</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="7">
@@ -2690,7 +2690,7 @@
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.shy._default[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.shy[1]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.shy._default[1]</t>
+          <t xml:space="preserve">fighter._default.shy[1]</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="8">
@@ -2722,7 +2722,7 @@
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.easygoing._default[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.easygoing._default[1]</t>
+          <t xml:space="preserve">fighter._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="9">
@@ -2754,7 +2754,7 @@
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.easygoing._default[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.easygoing._default[2]</t>
+          <t xml:space="preserve">fighter._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="9">
@@ -2786,7 +2786,7 @@
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.earnest._default[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.earnest[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.earnest._default[1]</t>
+          <t xml:space="preserve">fighter._default.earnest[1]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="10">
@@ -2818,7 +2818,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.earnest._default[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.earnest[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.earnest._default[2]</t>
+          <t xml:space="preserve">fighter._default.earnest[2]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="10">
@@ -2850,7 +2850,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.emotional._default[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.emotional[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.emotional._default[1]</t>
+          <t xml:space="preserve">fighter._default.emotional[1]</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="10">
@@ -2882,7 +2882,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.emotional._default[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter._default.emotional[2]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.emotional._default[2]</t>
+          <t xml:space="preserve">fighter._default.emotional[2]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="10">

--- a/セリフ編集/その他セリフ/18-経営危機・エンディング.xlsx
+++ b/セリフ編集/その他セリフ/18-経営危機・エンディング.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2466,7 +2466,7 @@
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.normal[1]</t>
+          <t xml:space="preserve">ENDING_LINES.coach[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2481,24 +2481,19 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter._default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">coach[1]</t>
         </is>
       </c>
       <c r="G72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体で戦えて、本当に良かった</t>
+          <t xml:space="preserve">よくぞここまで……立派になった</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.normal[2]</t>
+          <t xml:space="preserve">ENDING_LINES.coach[2]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2513,24 +2508,19 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter._default.normal[2]</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">coach[2]</t>
         </is>
       </c>
       <c r="G73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">入団した時は、まさかここまで来れるなんて思わなかった</t>
+          <t xml:space="preserve">あの選手たちを見ていると、指導者冥利に尽きる</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.normal[3]</t>
+          <t xml:space="preserve">ENDING_LINES.coach[3]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2545,24 +2535,19 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter._default.normal[3]</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">coach[3]</t>
         </is>
       </c>
       <c r="G74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の仲間と、最高の舞台。感謝しかないよ</t>
+          <t xml:space="preserve">私の教え子たちが業界の頂点に。これ以上の喜びはない</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.bold[1]</t>
+          <t xml:space="preserve">ENDING_LINES.coach[4]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2577,24 +2562,19 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">coach[4]</t>
         </is>
       </c>
       <c r="G75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが頂点？…でもまだ先がある気がする</t>
+          <t xml:space="preserve">まだまだ伸びる選手ばかりだ。楽しみは尽きないよ</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.bold[2]</t>
+          <t xml:space="preserve">ENDING_LINES.coach[5]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2609,24 +2589,19 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter._default.bold[2]</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">coach[5]</t>
         </is>
       </c>
       <c r="G76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで終わりじゃない。もっと強くなって、もっと上を目指す</t>
+          <t xml:space="preserve">ここが終着点じゃない。さらに上の景色を見せてやる</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.bold[3]</t>
+          <t xml:space="preserve">ENDING_LINES.coach[6]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2641,24 +2616,19 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter._default.bold[3]</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">coach[6]</t>
         </is>
       </c>
       <c r="G77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私たちの戦いが業界を変えたってことね。誇りに思うよ</t>
+          <t xml:space="preserve">選手たちの努力が実を結んだ。私は見守っただけだ</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.quiet[1]</t>
+          <t xml:space="preserve">ENDING_LINES.coach[7]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2673,24 +2643,19 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter._default.quiet[1]</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">coach[7]</t>
         </is>
       </c>
       <c r="G78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとうございました（静かに涙を流している）</t>
+          <t xml:space="preserve">苦しい時期を乗り越えた選手たちの姿に……涙が出そうだ</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.shy[1]</t>
+          <t xml:space="preserve">ENDING_LINES.coach[8]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2705,24 +2670,19 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter._default.shy[1]</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">coach[8]</t>
         </is>
       </c>
       <c r="G79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんなに幸せなことがあっていいのかな…</t>
+          <t xml:space="preserve">全員が成長した。一人の脱落者も出さなかった。それが誇りだ</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.easygoing[1]</t>
+          <t xml:space="preserve">ENDING_LINES.coach[9]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2737,24 +2697,19 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter._default.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">coach[9]</t>
         </is>
       </c>
       <c r="G80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで掴んだ頂点だ！最高のチームだよ！</t>
+          <t xml:space="preserve">この子たちとなら、もっと高い場所を目指せる</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.easygoing[2]</t>
+          <t xml:space="preserve">ENDING_LINES.coach[10]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2769,420 +2724,17 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter._default.easygoing[2]</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">coach[10]</t>
         </is>
       </c>
       <c r="G81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お金がなかった頃のことを思い出すと…よくここまで来たよね</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="40" customHeight="1">
-      <c r="A82" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fighter._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">練習してきたことが全部報われた。泣きそう</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="40" customHeight="1">
-      <c r="A83" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.earnest[2]</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fighter._default.earnest[2]</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あの時辞めなくてよかった。この瞬間のために全部あったんだ</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="40" customHeight="1">
-      <c r="A84" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fighter._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">涙が止まらない…！こんなに幸せなことがあっていいのかな…！</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="40" customHeight="1">
-      <c r="A85" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.fighter._default.emotional[2]</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fighter._default.emotional[2]</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">みんなありがとう…！最高だよ…！</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="40" customHeight="1">
-      <c r="A86" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.coach[1]</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">coach[1]</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">よくぞここまで……立派になった</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="40" customHeight="1">
-      <c r="A87" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.coach[2]</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">coach[2]</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あの選手たちを見ていると、指導者冥利に尽きる</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="40" customHeight="1">
-      <c r="A88" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.coach[3]</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">coach[3]</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">私の教え子たちが業界の頂点に。これ以上の喜びはない</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="40" customHeight="1">
-      <c r="A89" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.coach[4]</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">coach[4]</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">まだまだ伸びる選手ばかりだ。楽しみは尽きないよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="40" customHeight="1">
-      <c r="A90" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.coach[5]</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">coach[5]</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ここが終着点じゃない。さらに上の景色を見せてやる</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="40" customHeight="1">
-      <c r="A91" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.coach[6]</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">coach[6]</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">選手たちの努力が実を結んだ。私は見守っただけだ</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="40" customHeight="1">
-      <c r="A92" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.coach[7]</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">coach[7]</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">苦しい時期を乗り越えた選手たちの姿に……涙が出そうだ</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="40" customHeight="1">
-      <c r="A93" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.coach[8]</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">coach[8]</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">全員が成長した。一人の脱落者も出さなかった。それが誇りだ</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="40" customHeight="1">
-      <c r="A94" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.coach[9]</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">coach[9]</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">この子たちとなら、もっと高い場所を目指せる</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="40" customHeight="1">
-      <c r="A95" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.coach[10]</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">coach[10]</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">指導者として、これ以上の幸せはないよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I95"/>
+  <autoFilter ref="A1:I81"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
